--- a/data/trans_bre/IQ26A_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ26A_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,67</t>
+          <t>17,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>142,47%</t>
+          <t>127,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 5,11</t>
+          <t>-5,67; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 1,05</t>
+          <t>-9,61; 1,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 11,32</t>
+          <t>-2,12; 11,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 35,54</t>
+          <t>1,13; 36,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 92,94</t>
+          <t>-50,22; 89,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,08; 23,13</t>
+          <t>-76,09; 23,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 138,68</t>
+          <t>-16,36; 142,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 533,7</t>
+          <t>-6,43; 534,73</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,32%</t>
+          <t>-5,92%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 10,63</t>
+          <t>-1,21; 10,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 8,2</t>
+          <t>-1,25; 8,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,41</t>
+          <t>-5,29; 4,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 14,33</t>
+          <t>-15,74; 12,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 105,65</t>
+          <t>-7,92; 102,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 126,58</t>
+          <t>-12,74; 125,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,82; 54,0</t>
+          <t>-40,37; 51,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,65; 98,94</t>
+          <t>-59,51; 84,24</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 3,48</t>
+          <t>-7,9; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 5,13</t>
+          <t>-5,82; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 10,56</t>
+          <t>-3,63; 9,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 21,0</t>
+          <t>-10,54; 25,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 40,65</t>
+          <t>-51,88; 47,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 58,99</t>
+          <t>-41,23; 69,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 90,51</t>
+          <t>-19,15; 76,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 172,77</t>
+          <t>-40,24; 220,94</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>3,51</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 7,4</t>
+          <t>-4,26; 7,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 3,49</t>
+          <t>-8,46; 3,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 0,43</t>
+          <t>-11,96; -0,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 23,72</t>
+          <t>-11,45; 16,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 63,56</t>
+          <t>-24,46; 66,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 29,99</t>
+          <t>-47,95; 35,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,15; 3,9</t>
+          <t>-51,97; 0,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 246,68</t>
+          <t>-53,1; 175,56</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,51</t>
+          <t>-1,48; 4,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,18</t>
+          <t>-3,18; 2,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,97</t>
+          <t>-2,61; 3,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 14,41</t>
+          <t>-2,84; 13,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 41,51</t>
+          <t>-11,54; 41,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 22,75</t>
+          <t>-25,0; 27,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 23,99</t>
+          <t>-16,69; 27,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 95,36</t>
+          <t>-13,09; 91,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ26A_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ26A_R2-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,76</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-42,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>127,98%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.08606705822971628</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.162449510798261</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.07212080646967</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>17.76044031527241</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.01039386330900246</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4249537757877127</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.451641263408012</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.279788044995483</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,67; 5,42</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,61; 1,16</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,12; 11,91</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,13; 36,37</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-50,22; 89,85</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-76,09; 23,12</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-16,36; 142,13</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; 534,73</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.670816657152399</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.609029852614025</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.119029877198328</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.132619376981601</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5021991031182013</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7609209704487724</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1635575661382013</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.06427563767877667</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.416048802961047</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.155609593513825</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.90812481302779</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>36.37350197901325</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.8984708515988424</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2312223288588461</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.421292990430745</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>5.347314818720105</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,6</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,83%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-2,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-5,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,21; 10,03</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,25; 8,32</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,29; 4,29</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-15,74; 12,39</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-7,92; 102,54</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-12,74; 125,22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-40,37; 51,33</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-59,51; 84,24</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.598993712851041</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.253358085988718</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2681043887948598</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.254762965925435</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3682931357163475</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.3683078414540862</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.02489409971067303</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.05923572259526232</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,58</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-14,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>22,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>24,75%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.213177647125172</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.254222671587782</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.288819598446425</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-15.73809029740245</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.07916240088716794</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1273584112164228</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4036603495115418</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5951023121547958</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,9; 4,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,82; 5,52</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; 9,89</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-10,54; 25,47</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-51,88; 47,44</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-41,23; 69,78</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-19,15; 76,22</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-40,24; 220,94</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10.03416630644762</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.319815694530071</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.294217187179284</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>12.38817267511297</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.025381489186353</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.25217300340585</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.5132720972803761</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.8423700539381178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-6,06</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,51</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-17,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-30,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21,37%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.817338084844966</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.09561425249400984</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.577609188618636</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.302709732779118</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1490233291060062</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.008446070642819024</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.2266244250790482</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.2475342978307361</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,26; 7,68</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,46; 3,6</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-11,96; -0,05</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-11,45; 16,27</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-24,46; 66,62</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-47,95; 35,79</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-51,97; 0,61</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-53,1; 175,56</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.899733616364724</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.823464543688742</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.628786094454494</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-10.54249922630046</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5188401420308243</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4123372026824832</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1914705024229949</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4024360256156471</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.089470345837614</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.518874684684747</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.893882581563194</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>25.46547113124132</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.4743776685833881</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.6978181042947398</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.7621751725942656</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.209417564281403</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.574967838701205</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.503377356571646</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-6.063604773981046</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3.510329520883368</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1091690543995514</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1758953588691351</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.3031460251941366</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.213720209406699</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.257121740576754</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.456478660258639</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-11.96217100450517</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-11.45127654914779</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2445755070114631</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4795132616777356</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5196634194296891</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5309639636956982</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.684680416049733</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.598949350243948</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-0.04526893533075477</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>16.27133550519868</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.666201787146974</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.357893285648073</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.006140745585040921</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.755581676405422</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,85</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-5,19%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>25,93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,48; 4,56</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,18; 2,49</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 3,55</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 13,85</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-11,54; 41,56</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-25,0; 27,81</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-16,69; 27,58</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-13,09; 91,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.521405061564127</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5747571972734331</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04942356508404744</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>4.849190175198132</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1256190342268869</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.05189920856895015</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.003402635782513513</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.2592756608485701</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.483251179502405</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.179606397259212</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.611929340832301</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.840517901503463</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1154058823863851</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2499556037219895</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1668754702910007</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.130877930817925</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.564165250736426</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.485019826728827</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.547064705075733</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>13.8530238253774</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.4155584844073841</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2781159400673775</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.275846228217617</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.9152031828519622</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
